--- a/internal/doc/nursia-analytics-sprint-tracker.xlsx
+++ b/internal/doc/nursia-analytics-sprint-tracker.xlsx
@@ -3857,7 +3857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4286,8 +4286,66 @@
       </c>
       <c r="G16" s="5" t="inlineStr"/>
     </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Clarity tag (layout.tsx:138)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Script strategy</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>afterInteractive</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Currently beforeInteractive — executes ahead of hydration. NUR-21</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Tag management</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Adds a loader in front of existing tags; one blocked container kills all measurement at once, threatening DOD-1 and DOD-3. See PRD</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F5:F16">
+  <conditionalFormatting sqref="F5:F18">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -4298,7 +4356,7 @@
       <formula>"In progress"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D16">
+  <conditionalFormatting sqref="D5:D18">
     <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="1">
       <formula>4000</formula>
     </cfRule>
@@ -4308,8 +4366,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Not started,In progress,Blocked,In review,Done"</formula1>
+    <dataValidation sqref="F5:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Blocked,In review,Done,Decided"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/internal/doc/nursia-analytics-sprint-tracker.xlsx
+++ b/internal/doc/nursia-analytics-sprint-tracker.xlsx
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>signup, login, exam, try</t>
+          <t>signup, login, exam, try. Must carry gbraid + wbraid too</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1966,52 +1966,134 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Total points</t>
-        </is>
-      </c>
-      <c r="F30" s="7">
-        <f>SUM(F5:F28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Points done</t>
-        </is>
-      </c>
-      <c r="F31" s="8">
-        <f>SUMIF(G5:G28,"Done",F5:F28)</f>
-        <v/>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>NUR-24</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Google Ads Offline Conversion Import for purchase</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Google Ads API</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Upload gclid/gbraid/wbraid + value. Not a container</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NUR-25</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Send Meta Purchase through CAPI</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>src/app/api/meta/capi</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>value + currency, same event_id as PostHog</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>P0 points outstanding</t>
-        </is>
-      </c>
-      <c r="F32" s="9">
-        <f>SUMIFS(F5:F28,C5:C28,"P0",G5:G28,"&lt;&gt;Done")</f>
+          <t>Total points</t>
+        </is>
+      </c>
+      <c r="F32" s="7">
+        <f>SUM(F5:F30)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="E33" s="6" t="inlineStr">
         <is>
+          <t>Points done</t>
+        </is>
+      </c>
+      <c r="F33" s="8">
+        <f>SUMIF(G5:G30,"Done",F5:F30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>P0 points outstanding</t>
+        </is>
+      </c>
+      <c r="F34" s="9">
+        <f>SUMIFS(F5:F30,C5:C30,"P0",G5:G30,"&lt;&gt;Done")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
           <t>Percent complete</t>
         </is>
       </c>
-      <c r="F33" s="10">
-        <f>IF(F30=0,0,F31/F30)</f>
+      <c r="F35" s="10">
+        <f>IF(F32=0,0,F33/F32)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G28">
+  <conditionalFormatting sqref="G5:G30">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -2023,7 +2105,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Blocked,In review,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4380,7 +4462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4478,7 +4560,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Read utm_*, gclid, fbclid, src from the landing URL</t>
+          <t>Read utm_*, gclid, gbraid, wbraid, fbclid, src from the landing URL</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -4674,12 +4756,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Required for ROAS by channel</t>
+          <t>Required for ROAS by channel. Must carry the shared event_id so Meta and Ads can dedupe against it</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -4692,22 +4774,22 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>C-09</t>
+          <t>C-08b</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Add step_index to onboarding events</t>
+          <t>Expose purchase to the Ads upload job</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Else the onboarding funnel is unreadable</t>
+          <t>Purchase + stored gclid/gbraid/wbraid + timestamp, readable server-side for Offline Conversion Import</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -4720,17 +4802,17 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>C-10</t>
+          <t>C-09</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Add login_failed with a reason</t>
+          <t>Add step_index to onboarding events</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>101 login_viewed to 1 login_completed is currently unexplainable</t>
+          <t>Else the onboarding funnel is unreadable</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -4748,17 +4830,17 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>C-11</t>
+          <t>C-10</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Confirm the PostHog project matches</t>
+          <t>Add login_failed with a reason</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Must be 595036 or the funnel splits across projects</t>
+          <t>101 login_viewed to 1 login_completed is currently unexplainable</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -4776,22 +4858,22 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>C-12</t>
+          <t>C-11</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Remediate app entry LCP</t>
+          <t>Confirm the PostHog project matches</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>p75 4461ms against a 2500ms budget on the page every paid click reaches</t>
+          <t>Must be 595036 or the funnel splits across projects</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -4804,33 +4886,61 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>C-12</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Remediate app entry LCP</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>p75 4461ms against a 2500ms budget on the page every paid click reaches</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>C-13</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Agree a shared staging test plan</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Both sides verify before either ships</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E18">
+  <conditionalFormatting sqref="E5:E19">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -4841,7 +4951,7 @@
       <formula>"In progress"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D18">
+  <conditionalFormatting sqref="D5:D19">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
       <formula>"SECURITY"</formula>
     </cfRule>
@@ -4853,7 +4963,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
     </dataValidation>
   </dataValidations>

--- a/internal/doc/nursia-analytics-sprint-tracker.xlsx
+++ b/internal/doc/nursia-analytics-sprint-tracker.xlsx
@@ -11,9 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint board" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Area coverage" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event QA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PostHog dashboard" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance budget" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App contract" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PostHog install" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PostHog dashboard" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance budget" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App contract" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3503,6 +3504,591 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PostHog on nursia.io — install spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The single change that makes eight of the outcome rows answerable. The app already reports to project 595036; this side does not, so neither half can describe a whole customer. PH-03 and PH-10 are the two that fail quietly rather than loudly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>PH-01</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Proxy</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Add /ingest rewrites to next.config.ts</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Two rules: /ingest/static/:path* to us-assets.i.posthog.com/static, /ingest/:path* to us.i.posthog.com. Separate hosts — merging them breaks the SDK bundle or the recorder</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PH-02</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Proxy</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Set skipTrailingSlashRedirect: true</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Next would otherwise redirect /ingest/decide/ to /ingest/decide and drop the POST body with it</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>PH-03</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Init</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>api_host = '/ingest'</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Same-origin. us.i.posthog.com is blocked far more on paid/mobile than organic desktop, which would bias the exact comparison the dashboard exists to make. DOD-3 depends on this</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>PH-04</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Init</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>ui_host = 'https://us.posthog.com'</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Where 'open in PostHog' links resolve. Without it they point at the proxy path and 404</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PH-05</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Init</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>capture_pageview = 'history_change'</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>SDK watches the History API, so App Router navigation captures with no router subscription. The usePathname effect double-fires on first render and misses replaceState</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>PH-06</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Init</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>person_profiles = 'identified_only'</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Most marketing traffic never signs up. A profile per anonymous reader costs money and answers nothing</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>PH-07</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Init</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>capture_performance = { web_vitals: true }</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Field Core Web Vitals. DOD-5 is enforced against this rather than a Lighthouse run</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>PH-08</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Init</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>defaults pinned to '2026-08-30'</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Leaving defaults unset silently changes SDK behaviour on upgrade</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PH-09</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Attribution</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Capture first touch with register_once</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>utm_source/medium/campaign/content/term, gclid, gbraid, wbraid, fbclid, src — prefixed initial_</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>NUR-06</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>PH-10</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Attribution</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Do NOT use setPersonProperties for this</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Under identified_only it either no-ops or creates the anonymous profile the setting exists to avoid. register_once gives first-touch-wins at the storage layer, survives to $identify, and costs no profile</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>NUR-06</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PH-11</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Dual-send from the existing track() in analytics.ts</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>One edit sends all nine existing events. No change to any of the nine call sites</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>PH-12</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Add NEXT_PUBLIC_POSTHOG_KEY to .env.example</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Project token for NCLEX-Nursia (595036). Public by design, like the GA4 and Meta pixel ids already there</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>PH-13</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Gate on the key, not on NODE_ENV</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Unlike the other three tags. PostHog is the system of record; not seeing events in development is how instrumentation ships broken</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>PH-14</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Land NUR-21 (Clarity off beforeInteractive) first</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Buys budget headroom before a fourth script is added to the same pages</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>NUR-21</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>PH-15</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Measure p75 LCP for 7 days, compare to baseline</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>HARD GATE. A regression past +100ms reverts the ticket (DOD-5)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>NUR-22</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F5:F19">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"In progress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Blocked,In review,Done"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3933,7 +4519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4456,7 +5042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/internal/doc/nursia-analytics-sprint-tracker.xlsx
+++ b/internal/doc/nursia-analytics-sprint-tracker.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PostHog install" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PostHog dashboard" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance budget" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App contract" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GTM options" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App contract" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4996,18 +4997,18 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ENG CALL</t>
         </is>
       </c>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Adds a loader in front of existing tags; one blocked container kills all measurement at once, threatening DOD-1 and DOD-3. See PRD</t>
+          <t>Not recommended this sprint, but the decision is engineering's. See the GTM options sheet for loading strategies worth prototyping</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -5048,6 +5049,327 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Google Tag Manager — options for engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GTM does not improve Core Web Vitals; a container loads tags rather than replacing them. But the autonomy case is real, and these are the ways to load it without paying full price. The final decision is engineering's — record it in G-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Approach</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Owner / notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Server-side GTM</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Best outcome, highest setup cost</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Container runs on infrastructure you own. Browser makes one first-party request; tags fire server-side and ship no JS to the page. The only option that removes main-thread work rather than rescheduling it, and it solves blocking at the same time</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Needs a hosting decision</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>First-party container serving</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Cheap; do this either way</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Serve gtm.js from our own domain via a Next.js rewrite — same technique as NUR-05 for PostHog. Nothing for main-thread cost, but removes the correlated-blocking risk, which is the more serious problem</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Deferred container load</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Easy, real speed win, costs early events</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Load after LCP settles — requestIdleCallback, first interaction, or a timer via next/script lazyOnload. Keeps the container off the critical path. Events before load are missed unless queued; bounced sessions may never fire</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Web worker (Partytown)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Experimental — prototype before committing</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Next exposes an experimental worker script strategy. Attractive on paper, fragile in practice: tags touching DOM or cookies often break, and debugging is unpleasant. Verify every tag still fires</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>G-05</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Deliberately small container</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Free, requires ongoing discipline</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Most GTM performance complaints are container-bloat complaints. No custom HTML tags, no unused triggers, no vendor templates kept just in case, and a periodic prune</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>G-06</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Container in front of everything</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>NOT RECOMMENDED in any scenario</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Migrating GA4, Ads, Clarity, Meta Pixel AND PostHog behind one client-side container. Slowest and most fragile configuration, and it defeats NUR-05's same-origin proxy. If GTM is adopted, keep PostHog outside it</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>G-07</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Record the outcome here</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Recommendation is: not this sprint. Revisit when the tag list approaches ten or non-engineers need to ship pixels, and evaluate G-01 + G-02 together rather than a plain client container. Engineering decides</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F5:F11">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"In progress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,Exploring,Prototyped,Adopted,Rejected"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/internal/doc/nursia-analytics-sprint-tracker.xlsx
+++ b/internal/doc/nursia-analytics-sprint-tracker.xlsx
@@ -873,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2050,52 +2050,134 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Total points</t>
-        </is>
-      </c>
-      <c r="F32" s="7">
-        <f>SUM(F5:F30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Points done</t>
-        </is>
-      </c>
-      <c r="F33" s="8">
-        <f>SUMIF(G5:G30,"Done",F5:F30)</f>
-        <v/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>NUR-26</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Retire or repoint the Ads SECONDARY conversion</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>ADS_QUESTION_LABEL fires inside questionAnswered; dies with the preview. Second dead action in the account</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>NUR-27</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Decide the pre-registration engagement signal</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>This repo</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Finding 05. Keep one ungated question, or knowingly lose the tried-but-did-not-sign-up segment</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>P0 points outstanding</t>
-        </is>
-      </c>
-      <c r="F34" s="9">
-        <f>SUMIFS(F5:F30,C5:C30,"P0",G5:G30,"&lt;&gt;Done")</f>
+          <t>Total points</t>
+        </is>
+      </c>
+      <c r="F34" s="7">
+        <f>SUM(F5:F32)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="E35" s="6" t="inlineStr">
         <is>
+          <t>Points done</t>
+        </is>
+      </c>
+      <c r="F35" s="8">
+        <f>SUMIF(G5:G32,"Done",F5:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>P0 points outstanding</t>
+        </is>
+      </c>
+      <c r="F36" s="9">
+        <f>SUMIFS(F5:F32,C5:C32,"P0",G5:G32,"&lt;&gt;Done")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
           <t>Percent complete</t>
         </is>
       </c>
-      <c r="F35" s="10">
-        <f>IF(F32=0,0,F33/F32)</f>
+      <c r="F37" s="10">
+        <f>IF(F34=0,0,F35/F34)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G30">
+  <conditionalFormatting sqref="G5:G32">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -2107,7 +2189,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Blocked,In review,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2212,7 +2294,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>PostHog, tagged ad URLs</t>
+          <t>PostHog, tagged ad URLs. LPs need a new hook once the question demo goes</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -2382,7 +2464,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>app.nursia.io</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2392,7 +2474,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>GA4 only, capped at FREE_PREVIEW=2</t>
+          <t>Nothing — the GA4 preview is being withdrawn</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2845,17 +2927,17 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>nursia.io</t>
+          <t>app.nursia.io</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2865,12 +2947,12 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pending NUR-12</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Capped at FREE_PREVIEW=2. Absent in app</t>
+          <t>nursia.io preview being withdrawn (Finding 05); absent in app. Soon zero everywhere</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
@@ -4169,7 +4251,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>$pageview &gt; question_answered &gt; registration_completed &gt; activated &gt; practice_session_completed, breakdown by utm_source</t>
+          <t>$pageview &gt; registration_completed &gt; question_answered &gt; activated &gt; practice_session_completed, by utm_source. Note the order — questions now sit behind registration</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/internal/doc/nursia-analytics-sprint-tracker.xlsx
+++ b/internal/doc/nursia-analytics-sprint-tracker.xlsx
@@ -563,13 +563,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,7 +583,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Read this sheet first. Everything below is written for whoever funds the work, not only for whoever builds it.</t>
+          <t>Read this sheet first. The book serves two audiences: the 'Who reads this' column says which sheets are yours. Nothing here assumes you write code except where it says so.</t>
         </is>
       </c>
     </row>
@@ -603,6 +604,11 @@
           <t>Why it matters commercially</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Who reads this</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -621,6 +627,11 @@
           <t>Every pound of ad spend is currently unattributable to what it produced.</t>
         </is>
       </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -641,6 +652,11 @@
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Smart Bidding is optimising toward an event that never happens. It is buying blind.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
         </is>
       </c>
     </row>
@@ -661,6 +677,11 @@
           <t>Meta cannot learn what a good customer looks like, so delivery stays broad and expensive.</t>
         </is>
       </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="inlineStr"/>
@@ -679,6 +700,11 @@
           <t>Nobody can answer: which channel brings people who actually study?</t>
         </is>
       </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="4" t="inlineStr"/>
@@ -697,6 +723,11 @@
           <t>A stolen session is a customer breach. Fix first, before anything else ships.</t>
         </is>
       </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -717,6 +748,11 @@
       <c r="D10" s="6" t="inlineStr">
         <is>
           <t>After it: budget moves on evidence rather than on click-through rate.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
         </is>
       </c>
     </row>
@@ -737,6 +773,11 @@
           <t>Deciding them takes an hour. Not deciding them costs the sprint.</t>
         </is>
       </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -757,6 +798,11 @@
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Stops anyone declaring victory on instrumentation that does not work.</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
         </is>
       </c>
     </row>
@@ -777,6 +823,11 @@
           <t>Read before sprint planning, not during.</t>
         </is>
       </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Engineering + growth lead</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="inlineStr"/>
@@ -795,6 +846,11 @@
           <t>The 'Why it matters' column is the one to read if you do not write code.</t>
         </is>
       </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="4" t="inlineStr"/>
@@ -813,6 +869,11 @@
           <t>Shows at a glance which parts of the product are invisible.</t>
         </is>
       </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="4" t="inlineStr"/>
@@ -831,6 +892,11 @@
           <t>Tick nothing you have not seen with your own eyes.</t>
         </is>
       </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="4" t="inlineStr"/>
@@ -849,6 +915,11 @@
           <t>The dashboard is the deliverable. Everything else exists to fill it.</t>
         </is>
       </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Engineering / Growth</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="4" t="inlineStr"/>
@@ -867,6 +938,11 @@
           <t>A faster page converts better. The budget protects that while instrumentation is added.</t>
         </is>
       </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="4" t="inlineStr"/>
@@ -883,6 +959,11 @@
       <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Twelve tickets depend on it. Confirm ownership before sprint start or the sprint cannot finish.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Engineering (external team)</t>
         </is>
       </c>
     </row>
@@ -919,7 +1000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GTM does not improve Core Web Vitals; a container loads tags rather than replacing them. But the autonomy case is real, and these are the ways to load it without paying full price. The final decision is engineering's — record it in G-07.</t>
+          <t>FOR ENGINEERING, DECIDED BY ENGINEERING. GTM does not improve Core Web Vitals; a container loads tags rather than replacing them. But the autonomy case is real, and these are the ways to load it without paying full price. The final decision is engineering's — record it in G-07.</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1320,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Not our repository. Twelve of twenty-four sprint tickets depend on this team. C-00 is a security fix and does not wait; C-01 to C-07 block activation and high-intent measurement entirely.</t>
+          <t>FOR THE APP TEAM. Not our repository. Twelve of the sprint tickets depend on them. C-00 is a security fix and does not wait; C-01 to C-07 block activation and high-intent measurement entirely.</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1837,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>All six, or the sprint is not done. Each is measurable the day it is claimed, from a named surface. 'It looks right in DebugView' is not a gate.</t>
+          <t>FOR EVERYONE. All six, or the sprint is not done. Each is measurable the day it is claimed, from a named surface. 'It looks right in DebugView' is not a gate.</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2161,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each changes what gets built. Left undecided, each has a default that happens anyway — usually the worse one, chosen by whoever picks up the ticket first. Settled and NOT reopenable: dashboards are PostHog, Ads conversions stay on gtag, the six gates are the definition of done.</t>
+          <t>FOR ENGINEERING, WITH THE GROWTH LEAD. Each changes what gets built. Left undecided, each has a default that happens anyway — usually the worse one, chosen by whoever picks up the ticket first. Settled and NOT reopenable: dashboards are PostHog, Ads conversions stay on gtag, the six gates are the definition of done.</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>60 points across 28 tickets. NUR-00 is security and does not wait for the sprint. NUR-01 to NUR-10 are P0 and stop money being spent blind; if the sprint is cut, it is cut after those. Read the last column if you do not write code.</t>
+          <t>FOR EVERYONE. 60 points across 28 tickets. NUR-00 is security and does not wait for the sprint. NUR-01 to NUR-10 are P0 and stop money being spent blind; if the sprint is cut, it is cut after those. Read the last column if you do not write code.</t>
         </is>
       </c>
     </row>
@@ -3955,7 +4036,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Nine product areas, each with its own owner and its own gap. Status mirrors the rails in the PRD.</t>
+          <t>FOR EVERYONE. Nine product areas, each with its own owner and its own gap. Status mirrors the rails in the PRD.</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4459,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tick each column only after seeing the event in PostHog, GA4 DebugView and Meta Test Events. Status reflects the estate as audited on 11 Sep 2026, not intent.</t>
+          <t>FOR ENGINEERING. Tick each column only after seeing the event in PostHog, GA4 DebugView and Meta Test Events. Status reflects the estate as audited on 11 Sep 2026, not intent.</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5420,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The single change that makes eight of the outcome rows answerable. The app already reports to project 595036; this side does not, so neither half can describe a whole customer. PH-03 and PH-10 are the two that fail quietly rather than loudly.</t>
+          <t>FOR ENGINEERING. The single change that makes eight of the outcome rows answerable. The app already reports to project 595036; this side does not, so neither half can describe a whole customer. PH-03 and PH-10 are the two that fail quietly rather than loudly.</t>
         </is>
       </c>
     </row>
@@ -5924,7 +6005,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Project NCLEX-Nursia (595036). Eleven tiles. Tiles 6 and 10 need no new instrumentation — build those first so the dashboard exists and carries real data while the rest fills in.</t>
+          <t>FOR GROWTH AND ENGINEERING. This is the deliverable. Project NCLEX-Nursia (595036). Eleven tiles; 6 and 10 need no new instrumentation — build those first so the dashboard exists and carries real data while the rest fills in.</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6441,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Baseline p75 from PostHog $web_vitals, 30 days to 11 Sep 2026 (312 events, 17 people). Google thresholds: LCP good ≤2500ms / poor &gt;4000ms, CLS good ≤0.10, INP good ≤200ms.</t>
+          <t>FOR ENGINEERING. A faster page converts better, so this is a growth constraint enforced by engineers. Baseline p75 from PostHog $web_vitals, 30 days to 11 Sep 2026 (312 events, 17 people). Google thresholds: LCP good ≤2500ms / poor &gt;4000ms, CLS good ≤0.10, INP good ≤200ms.</t>
         </is>
       </c>
     </row>

--- a/internal/doc/nursia-analytics-sprint-tracker.xlsx
+++ b/internal/doc/nursia-analytics-sprint-tracker.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PostHog dashboard" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance budget" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GTM options" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App contract" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies &amp; keys" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App contract" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -563,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -737,12 +738,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>One sprint, 60 points, 28 tickets</t>
+          <t>One sprint, 71 points, 33 tickets</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>11 are P0 and stop money being spent blind. Twelve of the 28 belong to the app.nursia.io team and are a hard dependency.</t>
+          <t>14 are P0 and stop money being spent blind. Twelve of the 33 belong to the app.nursia.io team and are a hard dependency.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -838,7 +839,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>The 28 tickets, sequenced by dependency, with a growth rationale on each.</t>
+          <t>The 33 tickets, sequenced by dependency, with a growth rationale on each.</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -948,20 +949,43 @@
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>Dependencies &amp; keys</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Accounts, tokens and access the sprint needs, with lead times. The Google Ads developer token takes days to weeks.</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Apply for that one before sprint planning or revenue attribution cannot start.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Engineering + account admins</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>App contract</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>What the app.nursia.io team must build. Not our repository.</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Twelve tickets depend on it. Confirm ownership before sprint start or the sprint cannot finish.</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Engineering (external team)</t>
         </is>
@@ -1294,6 +1318,503 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Technical dependencies and environment keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FOR ENGINEERING, ARRANGED BY WHOEVER HAS ACCOUNT ACCESS. Every one of these has blocked a sprint somewhere. Cheap to arrange in advance, expensive to discover on day four. D-02 is the long pole — start it before sprint planning. Secrets never enter the repository.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Needed for</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Who provides it</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Lead time</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Meta system user + CAPI access token</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>NUR-08, NUR-10, NUR-25</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Business Manager admin</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Same day, needs the right admin role</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>SECRET — server only</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads API developer token</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>NUR-24</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Google, via the Ads account</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>DAYS TO WEEKS — application is reviewed. LONG POLE</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>SECRET</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads OAuth client + refresh token</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>NUR-24</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Cloud console + one consent flow</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>SECRET</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Conversion action for purchase</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>NUR-24</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Ads account</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Minutes, must exist before first upload</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Internal id</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>D-05</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>PostHog project token</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>NUR-05 and everything after</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Already exists — project 595036</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Public — ships to browser</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>D-06</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Supabase service access</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>E-02 canonical id, warehousing</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>App team</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>SECRET</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>D-07</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>app.nursia.io deploy slot</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>12 contract tickets</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>App team release process</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>UNKNOWN — confirm before sprint start</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Sanity write token</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Content seeding pipeline</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Sanity project admin</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Minutes</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>SECRET</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>D-09</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Search Console property + ownership</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Sitemap submission</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Whoever verified the domain</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Minutes if already verified</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>NEXT_PUBLIC_POSTHOG_KEY / _HOST</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>From D-05</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Public — goes in .env.example</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>META_TEST_EVENT_CODE</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>NUR-10, NUR-17</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Events Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Minutes</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Dev only — MUST be unset in production</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G5:G15">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"In progress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G5:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,Requested,Received,Configured"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2538,7 +3059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3943,52 +4464,282 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="E34" s="8" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>NUR-28</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Move login back onto nursia.io</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>src/app/(funnel)/login</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>The identity-rich moment currently sits past the boundary that destroys identity. Worth more than any other single change</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>Login is where an anonymous visitor becomes a known person. Doing it on the wrong domain is why 101 logins produced 1 completion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>NUR-29</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Enable PostHog session replay on nursia.io</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>src/app/layout.tsx</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Sampled, with the NUR-00 sanitiser. Turns a drop-off number into a reason</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>The funnel says Meta traffic drops at the gate. Replay says whether they scrolled past it, tapped and bounced, or never saw it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>NUR-30</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Apply for Google Ads API access (developer token)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>LONG POLE — review takes days to weeks. Blocks NUR-24. Apply before sprint planning</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Google review takes days to weeks and nothing about revenue attribution can start without it. Apply today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>NUR-31</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Document the pipeline env vars in .env.example</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>This repo</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>17 undocumented vars; only the author can run the seeding pipeline today</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Only one person can run the content pipeline today. That is a single point of failure on the growth engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>NUR-32</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Deploy Sanity Studio + wire the revalidate webhook</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>studio/</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Editors run it locally today, and edits reach the site on the next deploy rather than in seconds</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>An edit currently reaches the live site on the next deploy instead of in seconds, which makes content iteration slow enough to stop happening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Total points</t>
         </is>
       </c>
-      <c r="F34" s="9">
-        <f>SUM(F5:F32)</f>
+      <c r="F39" s="9">
+        <f>SUM(F5:F37)</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="E35" s="8" t="inlineStr">
+    <row r="40">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>Points done</t>
         </is>
       </c>
-      <c r="F35" s="10">
-        <f>SUMIF(G5:G32,"Done",F5:F32)</f>
+      <c r="F40" s="10">
+        <f>SUMIF(G5:G37,"Done",F5:F37)</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="E36" s="8" t="inlineStr">
+    <row r="41">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>P0 points outstanding</t>
         </is>
       </c>
-      <c r="F36" s="11">
-        <f>SUMIFS(F5:F32,C5:C32,"P0",G5:G32,"&lt;&gt;Done")</f>
+      <c r="F41" s="11">
+        <f>SUMIFS(F5:F37,C5:C37,"P0",G5:G37,"&lt;&gt;Done")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="E37" s="8" t="inlineStr">
+    <row r="42">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>Percent complete</t>
         </is>
       </c>
-      <c r="F37" s="12">
-        <f>IF(F34=0,0,F35/F34)</f>
+      <c r="F42" s="12">
+        <f>IF(F39=0,0,F40/F39)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G32">
+  <conditionalFormatting sqref="G5:G37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -4000,7 +4751,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Blocked,In review,Done"</formula1>
     </dataValidation>
   </dataValidations>

--- a/internal/doc/nursia-analytics-sprint-tracker.xlsx
+++ b/internal/doc/nursia-analytics-sprint-tracker.xlsx
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Emit purchase with value and currency</t>
+          <t>Value + currency on every conversion event</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Required for ROAS by channel. Must carry the shared event_id so Meta and Ads can dedupe against it</t>
+          <t>purchase carries the actual amount; registration, activated and practice_session_completed carry a modelled value. Plus the shared event_id so Meta and Ads dedupe against it</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Emit purchase with value and currency</t>
+          <t>Put value + currency on EVERY conversion event</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -4041,12 +4041,12 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>No ROAS computable until this exists</t>
+          <t>purchase = actual amount. registration/activated/high-intent = modelled. Without it both platforms can only count, never weigh</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>No revenue event means no return on ad spend, so every channel looks equally good forever.</t>
+          <t>Count-based bidding treats every signup as identical — the exact assumption this whole sprint exists to disprove. Value is what lets delivery prefer signups that become customers.</t>
         </is>
       </c>
     </row>

--- a/internal/doc/nursia-analytics-sprint-tracker.xlsx
+++ b/internal/doc/nursia-analytics-sprint-tracker.xlsx
@@ -738,12 +738,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>One sprint, 71 points, 33 tickets</t>
+          <t>One sprint, 79 points, 36 tickets</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>14 are P0 and stop money being spent blind. Twelve of the 33 belong to the app.nursia.io team and are a hard dependency.</t>
+          <t>13 are P0 and stop money being spent blind. Fifteen of the 36 belong to the app.nursia.io team and are a hard dependency.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>The 33 tickets, sequenced by dependency, with a growth rationale on each.</t>
+          <t>The 36 tickets, sequenced by dependency, with a growth rationale on each.</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>NUR-24</t>
+          <t>NUR-30 only (optional)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>DAYS TO WEEKS — application is reviewed. LONG POLE</t>
+          <t>Days to weeks — but NOT on the critical path. NUR-24 has three routes without it</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>NUR-24</t>
+          <t>NUR-30 only (optional)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1500,32 +1500,32 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Conversion action for purchase</t>
+          <t>Zapier connection to Google Ads + Meta</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>NUR-24</t>
+          <t>NUR-24, NUR-25 fallback</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Ads account</t>
+          <t>Zapier workspace owner</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Minutes, must exist before first upload</t>
+          <t>Minutes — offline conversion action, no API approval</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Internal id</t>
+          <t>OAuth via Zapier</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1537,32 +1537,32 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>PostHog project token</t>
+          <t>Conversion action for purchase</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>NUR-05 and everything after</t>
+          <t>NUR-24</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Already exists — project 595036</t>
+          <t>Ads account</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Minutes, must exist before first upload</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Public — ships to browser</t>
+          <t>Internal id</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1574,32 +1574,32 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Supabase service access</t>
+          <t>PostHog project token</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>E-02 canonical id, warehousing</t>
+          <t>NUR-05 and everything after</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>App team</t>
+          <t>Already exists — project 595036</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Hours</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>SECRET</t>
+          <t>Public — ships to browser</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1611,32 +1611,32 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>app.nursia.io deploy slot</t>
+          <t>Supabase service access</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>12 contract tickets</t>
+          <t>E-02 canonical id, warehousing</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>App team release process</t>
+          <t>App team</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>UNKNOWN — confirm before sprint start</t>
+          <t>Hours</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>SECRET</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -1648,32 +1648,32 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Sanity write token</t>
+          <t>app.nursia.io deploy slot</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Content seeding pipeline</t>
+          <t>12 contract tickets</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Sanity project admin</t>
+          <t>App team release process</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Minutes</t>
+          <t>UNKNOWN — confirm before sprint start</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>SECRET</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -1685,32 +1685,32 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>D-09</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Search Console property + ownership</t>
+          <t>Sanity write token</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Sitemap submission</t>
+          <t>Content seeding pipeline</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Whoever verified the domain</t>
+          <t>Sanity project admin</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Minutes if already verified</t>
+          <t>Minutes</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>SECRET</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -1722,32 +1722,32 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>D-09</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>NEXT_PUBLIC_POSTHOG_KEY / _HOST</t>
+          <t>Search Console property + ownership</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>NUR-05</t>
+          <t>Sitemap submission</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>From D-05</t>
+          <t>Whoever verified the domain</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Minutes if already verified</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Public — goes in .env.example</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1759,42 +1759,79 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>NEXT_PUBLIC_POSTHOG_KEY / _HOST</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>NUR-05</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>From D-05</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Public — goes in .env.example</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>D-11</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>META_TEST_EVENT_CODE</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>NUR-10, NUR-17</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Events Manager</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Minutes</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Dev only — MUST be unset in production</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G15">
+  <conditionalFormatting sqref="G5:G16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -1806,7 +1843,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,Requested,Received,Configured"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2165,17 +2202,17 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Add step_index to onboarding events</t>
+          <t>Onboarding step funnel</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Else the onboarding funnel is unreadable</t>
+          <t>onboarding_started; step_index + step_name + step_total on every step event; onboarding_step_completed with seconds_on_step; last_step_index on skipped. Viewed alone cannot separate someone who moved on from someone who quit</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -3059,7 +3096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4298,12 +4335,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Google Ads Offline Conversion Import for purchase</t>
+          <t>Purchase to Google Ads: Enhanced Conversions, or Zapier</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Google Ads API</t>
+          <t>Google Ads</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -4317,12 +4354,12 @@
       <c r="H29" s="6" t="inlineStr"/>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Upload gclid/gbraid/wbraid + value. Not a container</t>
+          <t>Neither needs API access. gtag+EC on the purchase page first; Zapier offline conversion as the no-code fallback</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Attributes revenue to the Google click that earned it, days later and on another domain.</t>
+          <t>Attributes revenue to the Google click that earned it, days later and on another domain — without waiting weeks for API approval.</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4606,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -4593,12 +4630,12 @@
       <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>LONG POLE — review takes days to weeks. Blocks NUR-24. Apply before sprint planning</t>
+          <t>NOT a blocker — NUR-24 has three routes that need no API. Apply only when upload volume makes them a chore</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Google review takes days to weeks and nothing about revenue attribution can start without it. Apply today.</t>
+          <t>Optional. Revenue attribution has three routes needing no API access at all, so this only earns its keep once uploads get frequent enough to automate.</t>
         </is>
       </c>
     </row>
@@ -4694,52 +4731,198 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>Total points</t>
-        </is>
-      </c>
-      <c r="F39" s="9">
-        <f>SUM(F5:F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>Points done</t>
-        </is>
-      </c>
-      <c r="F40" s="10">
-        <f>SUMIF(G5:G37,"Done",F5:F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>P0 points outstanding</t>
-        </is>
-      </c>
-      <c r="F41" s="11">
-        <f>SUMIFS(F5:F37,C5:C37,"P0",G5:G37,"&lt;&gt;Done")</f>
-        <v/>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>NUR-33</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Use GA4 recommended event names on the wire</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>sign_up, login, tutorial_begin/complete, begin_checkout, purchase, refund. Custom names populate no built-in GA4 report</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>GA4 only builds its Monetisation, Acquisition and conversion reports for events it recognises by name. A custom name gets an empty report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>NUR-34</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>GA4 purchase with transaction_id + value + currency</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>app.nursia.io</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>App team</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>transaction_id is what stops a refreshed confirmation page booking revenue twice. Unlocks Monetisation, ROAS, LTV</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>Without transaction_id a refreshed confirmation page books the revenue twice, and ROAS, LTV and value bidding all inherit the error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>NUR-35</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Onboarding step funnel: started + step_index + completed</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>app.nursia.io</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>App team</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>26 step events with no index means a 5-step funnel reads as 1 step repeated</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Today you can see people are in onboarding but never where they stop. This is the difference between a number and knowing which step to rewrite.</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="E42" s="8" t="inlineStr">
         <is>
+          <t>Total points</t>
+        </is>
+      </c>
+      <c r="F42" s="9">
+        <f>SUM(F5:F40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Points done</t>
+        </is>
+      </c>
+      <c r="F43" s="10">
+        <f>SUMIF(G5:G40,"Done",F5:F40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>P0 points outstanding</t>
+        </is>
+      </c>
+      <c r="F44" s="11">
+        <f>SUMIFS(F5:F40,C5:C40,"P0",G5:G40,"&lt;&gt;Done")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="E45" s="8" t="inlineStr">
+        <is>
           <t>Percent complete</t>
         </is>
       </c>
-      <c r="F42" s="12">
-        <f>IF(F39=0,0,F40/F39)</f>
+      <c r="F45" s="12">
+        <f>IF(F42=0,0,F43/F42)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G37">
+  <conditionalFormatting sqref="G5:G40">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Done"</formula>
     </cfRule>
@@ -4751,7 +4934,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Blocked,In review,Done"</formula1>
     </dataValidation>
   </dataValidations>
